--- a/donation_forms/044_university_scholarship_alumni_sponsorship_form--donation_forms.xlsx
+++ b/donation_forms/044_university_scholarship_alumni_sponsorship_form--donation_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -738,8 +738,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -767,12 +767,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'level_1:_$100-$499',_'value':_'1'}</t>
+          <t>level_1:_$100-$499</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Level 1: $100-$499', 'value': '1'}</t>
+          <t>Level 1: $100-$499</t>
         </is>
       </c>
     </row>
@@ -784,12 +784,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'level_2:_$500-$999',_'value':_'2'}</t>
+          <t>level_2:_$500-$999</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Level 2: $500-$999', 'value': '2'}</t>
+          <t>Level 2: $500-$999</t>
         </is>
       </c>
     </row>
@@ -801,12 +801,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'level_3:_$1,000_or_more',_'value':_'3'}</t>
+          <t>level_3:_$1,000_or_more</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Level 3: $1,000 or more', 'value': '3'}</t>
+          <t>Level 3: $1,000 or more</t>
         </is>
       </c>
     </row>
@@ -818,12 +818,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'arts',_'value':_'arts'}</t>
+          <t>arts</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Arts', 'value': 'arts'}</t>
+          <t>Arts</t>
         </is>
       </c>
     </row>
@@ -835,12 +835,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'science',_'value':_'science'}</t>
+          <t>science</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Science', 'value': 'science'}</t>
+          <t>Science</t>
         </is>
       </c>
     </row>
@@ -852,12 +852,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'language_and_literature',_'value':_'language_and_literature'}</t>
+          <t>language_and_literature</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Language and Literature', 'value': 'language_and_literature'}</t>
+          <t>Language and Literature</t>
         </is>
       </c>
     </row>
@@ -869,12 +869,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'business',_'value':_'business'}</t>
+          <t>business</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Business', 'value': 'business'}</t>
+          <t>Business</t>
         </is>
       </c>
     </row>
@@ -886,12 +886,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'health_and_medicine',_'value':_'health_and_medicine'}</t>
+          <t>health_and_medicine</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Health and Medicine', 'value': 'health_and_medicine'}</t>
+          <t>Health and Medicine</t>
         </is>
       </c>
     </row>
@@ -903,12 +903,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_6,_'label':_'history_and_culture',_'value':_'history_and_culture'}</t>
+          <t>history_and_culture</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 6, 'label': 'History and Culture', 'value': 'history_and_culture'}</t>
+          <t>History and Culture</t>
         </is>
       </c>
     </row>
@@ -920,12 +920,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_7,_'label':_'technology',_'value':_'technology'}</t>
+          <t>technology</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 7, 'label': 'Technology', 'value': 'technology'}</t>
+          <t>Technology</t>
         </is>
       </c>
     </row>
@@ -937,12 +937,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_8,_'label':_'engineering',_'value':_'engineering'}</t>
+          <t>engineering</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 8, 'label': 'Engineering', 'value': 'engineering'}</t>
+          <t>Engineering</t>
         </is>
       </c>
     </row>
@@ -954,12 +954,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_9,_'label':_'social_sciences_and_humanities',_'value':_'social_sciences_and_humanities'}</t>
+          <t>social_sciences_and_humanities</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 9, 'label': 'Social Sciences and Humanities', 'value': 'social_sciences_and_humanities'}</t>
+          <t>Social Sciences and Humanities</t>
         </is>
       </c>
     </row>
@@ -971,12 +971,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_10,_'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 10, 'label': 'Other', 'value': 'other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
